--- a/output/pdf_financials_xlsx/GXLD.xlsx
+++ b/output/pdf_financials_xlsx/GXLD.xlsx
@@ -2209,16 +2209,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.017483</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.036673</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.07882400000000001</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.111655</v>
       </c>
     </row>
     <row r="93">
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.024482</v>
+        <v>-0.100459</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.261887</v>
+        <v>0.139754</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>-0.031097</v>
@@ -3552,7 +3552,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3838,7 +3842,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.017483</v>
       </c>
@@ -5060,7 +5068,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>-0.124941</v>
       </c>

--- a/output/pdf_financials_xlsx/GXLD.xlsx
+++ b/output/pdf_financials_xlsx/GXLD.xlsx
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001946</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005085</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003947</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
     </row>
     <row r="13">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.156168</v>
+        <v>-0.158114</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.446395</v>
+        <v>-0.45148</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.224309</v>
+        <v>-0.228256</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.680027</v>
+        <v>-0.6800310000000001</v>
       </c>
     </row>
     <row r="28">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.156168</v>
+        <v>-0.158114</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.446395</v>
+        <v>-0.45148</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.224309</v>
+        <v>-0.228256</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.680027</v>
+        <v>-0.6800310000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1083,10 +1083,10 @@
         <v>0.094403</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.032333</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.171674</v>
       </c>
     </row>
     <row r="35">
@@ -1121,10 +1121,10 @@
         <v>0.094403</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.032333</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.171674</v>
       </c>
     </row>
     <row r="37">
@@ -1349,10 +1349,10 @@
         <v>0.048407</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.041621</v>
+        <v>0.009287999999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.280425</v>
+        <v>0.108751</v>
       </c>
     </row>
     <row r="49">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">

--- a/output/pdf_financials_xlsx/GXLD.xlsx
+++ b/output/pdf_financials_xlsx/GXLD.xlsx
@@ -550,10 +550,10 @@
         <v>0.165146</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.115471</v>
+        <v>0.145471</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.455734</v>
+        <v>0.485734</v>
       </c>
     </row>
     <row r="8">
@@ -607,10 +607,10 @@
         <v>0.165906</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.115823</v>
+        <v>0.145823</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.462768</v>
+        <v>0.492768</v>
       </c>
     </row>
     <row r="11">
@@ -5570,7 +5570,11 @@
           <t>Director fees 5</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
